--- a/sample_leads_populated.xlsx
+++ b/sample_leads_populated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$H$13</definedName>
@@ -124,6 +124,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CRM</author>
+  </authors>
+  <commentList>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Enter an RTO code (kl05), office name (Kottayam), or both (KL-05 Kottayam). Close spelling matches are accepted; ambiguous values need review.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -415,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -426,6 +441,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,6 +485,11 @@
           <t>Enquiry Date</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>RTO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4977,5 +4998,6 @@
   </sheetData>
   <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/sample_leads_populated.xlsx
+++ b/sample_leads_populated.xlsx
@@ -447,42 +447,42 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>source</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>campaign</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>model</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>city</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Enquiry Date</t>
+          <t>enquiry date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
